--- a/Region_data.xlsx
+++ b/Region_data.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\GITHUBS\contact_wire_test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\githubs\contact_wire_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10EDBCF-B325-4454-BC07-C5291AA3538C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8372ADEF-D2CF-4082-840D-0EB2DB92683A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{62DB6618-FD48-415E-A163-826BF443D327}"/>
+    <workbookView xWindow="3645" yWindow="1425" windowWidth="21195" windowHeight="13020" activeTab="4" xr2:uid="{62DB6618-FD48-415E-A163-826BF443D327}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="carlisle_NS" sheetId="2" r:id="rId2"/>
-    <sheet name="carlisle_operators" sheetId="6" r:id="rId3"/>
-    <sheet name="carlisle_notes" sheetId="8" r:id="rId4"/>
+    <sheet name="blank_NS" sheetId="9" r:id="rId2"/>
+    <sheet name="blank_operators" sheetId="10" r:id="rId3"/>
+    <sheet name="carlisle_NS" sheetId="2" r:id="rId4"/>
+    <sheet name="carlisle_operators" sheetId="6" r:id="rId5"/>
+    <sheet name="carlisle_notes" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -258,9 +260,6 @@
     <t>Asset_Number</t>
   </si>
   <si>
-    <t>First_name</t>
-  </si>
-  <si>
     <t>Second_Name</t>
   </si>
   <si>
@@ -334,6 +333,9 @@
   </si>
   <si>
     <t>tb</t>
+  </si>
+  <si>
+    <t>First_Name</t>
   </si>
 </sst>
 </file>
@@ -396,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -409,15 +411,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -858,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{783AD9A3-ACBB-491E-9CBD-232643A794C9}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -870,7 +867,7 @@
     <col min="7" max="7" width="33" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -892,10 +889,8 @@
       <c r="G1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
@@ -914,13 +909,11 @@
       <c r="F2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="7">
         <v>1651371</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
@@ -939,13 +932,11 @@
       <c r="F3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="7">
         <v>1651372</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -964,13 +955,11 @@
       <c r="F4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="7">
         <v>1651373</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
@@ -989,13 +978,11 @@
       <c r="F5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="7">
         <v>1651374</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
@@ -1014,13 +1001,11 @@
       <c r="F6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="7">
         <v>1651375</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
@@ -1039,13 +1024,11 @@
       <c r="F7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="7">
         <v>1651376</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
@@ -1064,13 +1047,11 @@
       <c r="F8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="7">
         <v>1651377</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>10</v>
       </c>
@@ -1089,13 +1070,11 @@
       <c r="F9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="7">
         <v>1651343</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
@@ -1114,13 +1093,11 @@
       <c r="F10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="7">
         <v>1792244</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>14</v>
       </c>
@@ -1139,13 +1116,11 @@
       <c r="F11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="7">
         <v>1792235</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
@@ -1164,13 +1139,11 @@
       <c r="F12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="7">
         <v>1792229</v>
       </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
@@ -1189,99 +1162,9 @@
       <c r="F13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="7">
         <v>1792228</v>
       </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1295,6 +1178,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173102BE-C506-4420-B54D-D84F838C1734}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3FBB49D-575E-4C58-842E-5A9508A31FF9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AB5F898-7261-4E7F-87D8-D4BBEBAD440A}">
   <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1309,32 +1210,32 @@
     <col min="13" max="13" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="12"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1679,7 +1580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8969DD6-61AF-495A-B637-779D81187039}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1691,27 +1592,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
         <v>76</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>77</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>78</v>
       </c>
-      <c r="D1" t="s">
-        <v>79</v>
-      </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" t="s">
         <v>80</v>
-      </c>
-      <c r="B2" t="s">
-        <v>81</v>
       </c>
       <c r="C2">
         <v>140968</v>
@@ -1720,15 +1621,15 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3">
         <v>150270</v>
@@ -1737,15 +1638,15 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" t="s">
         <v>85</v>
-      </c>
-      <c r="B4" t="s">
-        <v>86</v>
       </c>
       <c r="C4">
         <v>74157</v>
@@ -1754,15 +1655,15 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" t="s">
         <v>88</v>
-      </c>
-      <c r="B5" t="s">
-        <v>89</v>
       </c>
       <c r="C5">
         <v>141012</v>
@@ -1771,15 +1672,15 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6">
         <v>116105</v>
@@ -1788,15 +1689,15 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" t="s">
         <v>93</v>
-      </c>
-      <c r="B7" t="s">
-        <v>94</v>
       </c>
       <c r="C7">
         <v>143208</v>
@@ -1805,15 +1706,15 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" t="s">
         <v>95</v>
-      </c>
-      <c r="B8" t="s">
-        <v>96</v>
       </c>
       <c r="C8">
         <v>1111595</v>
@@ -1822,15 +1723,15 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" t="s">
         <v>97</v>
-      </c>
-      <c r="B9" t="s">
-        <v>98</v>
       </c>
       <c r="C9">
         <v>1259055</v>
@@ -1839,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1847,7 +1748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A902736F-6C1B-4BCD-8EC7-2B50226ACF9C}">
   <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1862,32 +1763,32 @@
     <col min="13" max="13" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="12"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -2435,23 +2336,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="cb6380d2-b01f-4e04-9200-9666676ed141" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002A49252DC7531642B064D59214E738D4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2e90bbfbf4f52bf4a6656f5589d033bb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="cb6380d2-b01f-4e04-9200-9666676ed141" xmlns:ns4="f068c7d5-04e7-4821-88a1-b1f97a388bb7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d814bd8026fe29e70e1bc18c824ed2a7" ns3:_="" ns4:_="">
     <xsd:import namespace="cb6380d2-b01f-4e04-9200-9666676ed141"/>
@@ -2704,32 +2588,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A62760-3B76-45B2-B7CB-74304B7ECF2A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="f068c7d5-04e7-4821-88a1-b1f97a388bb7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="cb6380d2-b01f-4e04-9200-9666676ed141"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC417360-1F6A-4D75-9B30-CA996FA04E31}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="cb6380d2-b01f-4e04-9200-9666676ed141" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6848DD44-78B0-4924-8517-B02B8138DA94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2746,4 +2622,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC417360-1F6A-4D75-9B30-CA996FA04E31}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A62760-3B76-45B2-B7CB-74304B7ECF2A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="f068c7d5-04e7-4821-88a1-b1f97a388bb7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="cb6380d2-b01f-4e04-9200-9666676ed141"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Region_data.xlsx
+++ b/Region_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\githubs\contact_wire_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8372ADEF-D2CF-4082-840D-0EB2DB92683A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CCF52C-BCED-4D9D-83AC-EAFF38DA1361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3645" yWindow="1425" windowWidth="21195" windowHeight="13020" activeTab="4" xr2:uid="{62DB6618-FD48-415E-A163-826BF443D327}"/>
+    <workbookView xWindow="32925" yWindow="1500" windowWidth="21195" windowHeight="13020" activeTab="4" xr2:uid="{62DB6618-FD48-415E-A163-826BF443D327}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="91">
   <si>
     <t>neutral section names</t>
   </si>
@@ -260,72 +260,21 @@
     <t>Asset_Number</t>
   </si>
   <si>
-    <t>Second_Name</t>
-  </si>
-  <si>
     <t>Sentinal</t>
   </si>
   <si>
     <t>Level</t>
   </si>
   <si>
-    <t>Jim</t>
-  </si>
-  <si>
-    <t>Evans</t>
-  </si>
-  <si>
     <t>PW</t>
   </si>
   <si>
-    <t>dh</t>
-  </si>
-  <si>
-    <t>Mark</t>
-  </si>
-  <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>Hetherington</t>
-  </si>
-  <si>
     <t>kh</t>
   </si>
   <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Barrett</t>
-  </si>
-  <si>
     <t>cb</t>
   </si>
   <si>
-    <t>Hamilton</t>
-  </si>
-  <si>
-    <t>Karl</t>
-  </si>
-  <si>
-    <t>Luke</t>
-  </si>
-  <si>
-    <t>Scott</t>
-  </si>
-  <si>
-    <t>Sarah</t>
-  </si>
-  <si>
-    <t>Bar</t>
-  </si>
-  <si>
-    <t>Terance</t>
-  </si>
-  <si>
-    <t>Brown</t>
-  </si>
-  <si>
     <t>ls</t>
   </si>
   <si>
@@ -335,7 +284,25 @@
     <t>tb</t>
   </si>
   <si>
-    <t>First_Name</t>
+    <t>Kevin Hetherington</t>
+  </si>
+  <si>
+    <t>Charlotte Barrett</t>
+  </si>
+  <si>
+    <t>Karl Hamilton</t>
+  </si>
+  <si>
+    <t>Luke Scott</t>
+  </si>
+  <si>
+    <t>Sarah Bar</t>
+  </si>
+  <si>
+    <t>Terance Brown</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
 </sst>
 </file>
@@ -1582,17 +1549,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8969DD6-61AF-495A-B637-779D81187039}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s">
         <v>76</v>
@@ -1603,144 +1569,89 @@
       <c r="D1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2">
+        <v>74157</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>79</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3">
+        <v>141012</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>80</v>
       </c>
-      <c r="C2">
-        <v>140968</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3">
-        <v>150270</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="B4">
+        <v>116105</v>
       </c>
       <c r="C4">
-        <v>74157</v>
-      </c>
-      <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>87</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5">
+        <v>143208</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>88</v>
       </c>
-      <c r="C5">
-        <v>141012</v>
-      </c>
-      <c r="D5">
+      <c r="B6">
+        <v>1111595</v>
+      </c>
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6">
-        <v>116105</v>
-      </c>
-      <c r="D6">
+      <c r="B7">
+        <v>1259055</v>
+      </c>
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7">
-        <v>143208</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8">
-        <v>1111595</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9">
-        <v>1259055</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>100</v>
+      <c r="D7" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2336,6 +2247,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="cb6380d2-b01f-4e04-9200-9666676ed141" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002A49252DC7531642B064D59214E738D4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2e90bbfbf4f52bf4a6656f5589d033bb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="cb6380d2-b01f-4e04-9200-9666676ed141" xmlns:ns4="f068c7d5-04e7-4821-88a1-b1f97a388bb7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d814bd8026fe29e70e1bc18c824ed2a7" ns3:_="" ns4:_="">
     <xsd:import namespace="cb6380d2-b01f-4e04-9200-9666676ed141"/>
@@ -2588,24 +2516,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A62760-3B76-45B2-B7CB-74304B7ECF2A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="f068c7d5-04e7-4821-88a1-b1f97a388bb7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="cb6380d2-b01f-4e04-9200-9666676ed141"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="cb6380d2-b01f-4e04-9200-9666676ed141" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC417360-1F6A-4D75-9B30-CA996FA04E31}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6848DD44-78B0-4924-8517-B02B8138DA94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2622,29 +2558,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC417360-1F6A-4D75-9B30-CA996FA04E31}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A62760-3B76-45B2-B7CB-74304B7ECF2A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="f068c7d5-04e7-4821-88a1-b1f97a388bb7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="cb6380d2-b01f-4e04-9200-9666676ed141"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Region_data.xlsx
+++ b/Region_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\githubs\contact_wire_test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\GITHUBS\contact_wire_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CCF52C-BCED-4D9D-83AC-EAFF38DA1361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB04D36-D94D-402F-92F1-B1C3B6830584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32925" yWindow="1500" windowWidth="21195" windowHeight="13020" activeTab="4" xr2:uid="{62DB6618-FD48-415E-A163-826BF443D327}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{62DB6618-FD48-415E-A163-826BF443D327}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="carlisle_NS" sheetId="2" r:id="rId4"/>
     <sheet name="carlisle_operators" sheetId="6" r:id="rId5"/>
     <sheet name="carlisle_notes" sheetId="8" r:id="rId6"/>
+    <sheet name="test_NS" sheetId="13" r:id="rId7"/>
+    <sheet name="test_operators" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="91">
   <si>
     <t>neutral section names</t>
   </si>
@@ -2246,6 +2248,503 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03532AA-7E68-4D27-815B-0AAAF667291B}">
+  <dimension ref="A1:O13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" customWidth="1"/>
+    <col min="8" max="9" width="18.28515625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="9"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2100</v>
+      </c>
+      <c r="D2" s="2">
+        <v>107</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="3">
+        <v>2698638</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1100</v>
+      </c>
+      <c r="D3" s="2">
+        <v>107</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="3">
+        <v>2698639</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2100</v>
+      </c>
+      <c r="D4" s="2">
+        <v>107</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2689967</v>
+      </c>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1100</v>
+      </c>
+      <c r="D5" s="2">
+        <v>107</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="3">
+        <v>2689966</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2100</v>
+      </c>
+      <c r="D6" s="2">
+        <v>107</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2698641</v>
+      </c>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1100</v>
+      </c>
+      <c r="D7" s="2">
+        <v>107</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2698640</v>
+      </c>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2200</v>
+      </c>
+      <c r="D8" s="2">
+        <v>107</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2698643</v>
+      </c>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D9" s="2">
+        <v>107</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2698642</v>
+      </c>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2100</v>
+      </c>
+      <c r="D10" s="2">
+        <v>107</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2698636</v>
+      </c>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1100</v>
+      </c>
+      <c r="D11" s="2">
+        <v>107</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="3">
+        <v>2698637</v>
+      </c>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2100</v>
+      </c>
+      <c r="D12" s="2">
+        <v>107</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2758210</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1100</v>
+      </c>
+      <c r="D13" s="2">
+        <v>107</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="3">
+        <v>2758211</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F079C3F8-ED02-4984-9DDF-C8AC6032F290}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2">
+        <v>74157</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3">
+        <v>141012</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4">
+        <v>116105</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5">
+        <v>143208</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6">
+        <v>1111595</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7">
+        <v>1259055</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2255,15 +2754,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002A49252DC7531642B064D59214E738D4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2e90bbfbf4f52bf4a6656f5589d033bb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="cb6380d2-b01f-4e04-9200-9666676ed141" xmlns:ns4="f068c7d5-04e7-4821-88a1-b1f97a388bb7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d814bd8026fe29e70e1bc18c824ed2a7" ns3:_="" ns4:_="">
     <xsd:import namespace="cb6380d2-b01f-4e04-9200-9666676ed141"/>
@@ -2516,6 +3006,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A62760-3B76-45B2-B7CB-74304B7ECF2A}">
   <ds:schemaRefs>
@@ -2534,14 +3033,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC417360-1F6A-4D75-9B30-CA996FA04E31}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6848DD44-78B0-4924-8517-B02B8138DA94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2558,4 +3049,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC417360-1F6A-4D75-9B30-CA996FA04E31}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>